--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/19.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/19.xlsx
@@ -426,13 +426,13 @@
         <v>-19.02033721997189</v>
       </c>
       <c r="E2">
-        <v>-33.82711194814717</v>
+        <v>-29.68738705590228</v>
       </c>
       <c r="F2">
-        <v>-5.476007511844869</v>
+        <v>-4.858993311630788</v>
       </c>
       <c r="G2">
-        <v>-20.81997901005282</v>
+        <v>-19.60103283194763</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.57991722013409</v>
       </c>
       <c r="E3">
-        <v>-34.16151484700659</v>
+        <v>-29.65881917762489</v>
       </c>
       <c r="F3">
-        <v>-5.290797064299015</v>
+        <v>-5.40434957028898</v>
       </c>
       <c r="G3">
-        <v>-21.02920714340753</v>
+        <v>-18.94770991195462</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.10324502032152</v>
       </c>
       <c r="E4">
-        <v>-33.99581798306593</v>
+        <v>-30.71957572189261</v>
       </c>
       <c r="F4">
-        <v>-5.354027314825892</v>
+        <v>-5.111295876578319</v>
       </c>
       <c r="G4">
-        <v>-20.99109779843221</v>
+        <v>-18.52341218764116</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.61632251551076</v>
       </c>
       <c r="E5">
-        <v>-34.24332172995515</v>
+        <v>-30.17715057677984</v>
       </c>
       <c r="F5">
-        <v>-5.417564804300365</v>
+        <v>-5.154603106688969</v>
       </c>
       <c r="G5">
-        <v>-20.86824179819708</v>
+        <v>-18.5657888258166</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.13324444054059</v>
       </c>
       <c r="E6">
-        <v>-34.59247613289455</v>
+        <v>-30.76534953716214</v>
       </c>
       <c r="F6">
-        <v>-5.266244871491956</v>
+        <v>-5.116689187073348</v>
       </c>
       <c r="G6">
-        <v>-20.60888869483227</v>
+        <v>-18.92172212947134</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.67084716361832</v>
       </c>
       <c r="E7">
-        <v>-35.14468957457489</v>
+        <v>-31.0096267463209</v>
       </c>
       <c r="F7">
-        <v>-5.331430206971445</v>
+        <v>-5.26861567924737</v>
       </c>
       <c r="G7">
-        <v>-20.61484271098465</v>
+        <v>-18.66165560354281</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.24352898030216</v>
       </c>
       <c r="E8">
-        <v>-35.20820368676947</v>
+        <v>-31.84976056540892</v>
       </c>
       <c r="F8">
-        <v>-5.50614939468047</v>
+        <v>-5.243200366716398</v>
       </c>
       <c r="G8">
-        <v>-20.46694243374494</v>
+        <v>-18.29467500942352</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.86637918583516</v>
       </c>
       <c r="E9">
-        <v>-35.5227175277872</v>
+        <v>-31.70529771609023</v>
       </c>
       <c r="F9">
-        <v>-5.397884090889199</v>
+        <v>-4.816543658273348</v>
       </c>
       <c r="G9">
-        <v>-19.90370442369381</v>
+        <v>-17.765714387886</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.54831022968429</v>
       </c>
       <c r="E10">
-        <v>-36.08021569863449</v>
+        <v>-32.17189129970755</v>
       </c>
       <c r="F10">
-        <v>-5.390913409302392</v>
+        <v>-5.098204171628339</v>
       </c>
       <c r="G10">
-        <v>-19.49741275656844</v>
+        <v>-18.54942976503429</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.29483530453355</v>
       </c>
       <c r="E11">
-        <v>-36.35442612098395</v>
+        <v>-32.84202620454763</v>
       </c>
       <c r="F11">
-        <v>-5.2540479603842</v>
+        <v>-4.950697802664308</v>
       </c>
       <c r="G11">
-        <v>-19.37435150250988</v>
+        <v>-18.70064886417712</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.10621262258889</v>
       </c>
       <c r="E12">
-        <v>-37.1235534676317</v>
+        <v>-34.07169256506445</v>
       </c>
       <c r="F12">
-        <v>-5.442661791942334</v>
+        <v>-4.758808075420088</v>
       </c>
       <c r="G12">
-        <v>-19.18419542200692</v>
+        <v>-16.96164908730782</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.97454139345006</v>
       </c>
       <c r="E13">
-        <v>-37.07736303275347</v>
+        <v>-34.21294019783769</v>
       </c>
       <c r="F13">
-        <v>-5.190798705386337</v>
+        <v>-4.465764675797876</v>
       </c>
       <c r="G13">
-        <v>-18.78550973325802</v>
+        <v>-16.58180040267738</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.89616916969895</v>
       </c>
       <c r="E14">
-        <v>-37.24675965995839</v>
+        <v>-33.72759646759161</v>
       </c>
       <c r="F14">
-        <v>-5.128845713680261</v>
+        <v>-4.86345144378275</v>
       </c>
       <c r="G14">
-        <v>-18.50652343957256</v>
+        <v>-16.72597300563987</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.85970405476169</v>
       </c>
       <c r="E15">
-        <v>-37.63920401017412</v>
+        <v>-35.33017360569207</v>
       </c>
       <c r="F15">
-        <v>-5.211801813236895</v>
+        <v>-4.595832067074046</v>
       </c>
       <c r="G15">
-        <v>-18.54368596852365</v>
+        <v>-15.94492923874177</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.85196260314883</v>
       </c>
       <c r="E16">
-        <v>-38.72296067392679</v>
+        <v>-35.48011138008603</v>
       </c>
       <c r="F16">
-        <v>-5.03168218835622</v>
+        <v>-4.534191065433311</v>
       </c>
       <c r="G16">
-        <v>-18.0741794343259</v>
+        <v>-16.06053017842759</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.85918946761746</v>
       </c>
       <c r="E17">
-        <v>-39.28332763305794</v>
+        <v>-36.11119272508396</v>
       </c>
       <c r="F17">
-        <v>-5.070316694163365</v>
+        <v>-4.538365714226409</v>
       </c>
       <c r="G17">
-        <v>-17.9591942561104</v>
+        <v>-16.01061211751368</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.86837894982971</v>
       </c>
       <c r="E18">
-        <v>-39.37218535003645</v>
+        <v>-35.97324634986231</v>
       </c>
       <c r="F18">
-        <v>-4.988074845974594</v>
+        <v>-3.958296997460657</v>
       </c>
       <c r="G18">
-        <v>-17.64010070321666</v>
+        <v>-15.65890638051259</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.86841744005732</v>
       </c>
       <c r="E19">
-        <v>-40.13451092872468</v>
+        <v>-37.26829028962786</v>
       </c>
       <c r="F19">
-        <v>-4.718095747451886</v>
+        <v>-3.863989685755111</v>
       </c>
       <c r="G19">
-        <v>-17.4439972276524</v>
+        <v>-15.31608780301167</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.85054985076573</v>
       </c>
       <c r="E20">
-        <v>-40.49402421595663</v>
+        <v>-37.6521803524431</v>
       </c>
       <c r="F20">
-        <v>-4.820631995094056</v>
+        <v>-3.422280644438767</v>
       </c>
       <c r="G20">
-        <v>-17.3289789439815</v>
+        <v>-15.77579015659487</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.80850663524448</v>
       </c>
       <c r="E21">
-        <v>-40.90272352362289</v>
+        <v>-37.99911127464473</v>
       </c>
       <c r="F21">
-        <v>-4.437165322523914</v>
+        <v>-3.690579430985195</v>
       </c>
       <c r="G21">
-        <v>-17.46861278900965</v>
+        <v>-15.01979066670136</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.7368195839003</v>
       </c>
       <c r="E22">
-        <v>-40.85575645545233</v>
+        <v>-38.28834717375164</v>
       </c>
       <c r="F22">
-        <v>-4.389026997518216</v>
+        <v>-3.432914437807986</v>
       </c>
       <c r="G22">
-        <v>-17.42067112378269</v>
+        <v>-14.61066020677607</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.63716756825845</v>
       </c>
       <c r="E23">
-        <v>-41.13810001711957</v>
+        <v>-38.42820456500453</v>
       </c>
       <c r="F23">
-        <v>-4.284842112018074</v>
+        <v>-3.022480420909741</v>
       </c>
       <c r="G23">
-        <v>-17.15217263836564</v>
+        <v>-15.70451576640713</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.51069777856975</v>
       </c>
       <c r="E24">
-        <v>-41.76068594487911</v>
+        <v>-37.54930700841085</v>
       </c>
       <c r="F24">
-        <v>-4.14506739533322</v>
+        <v>-2.931030906528605</v>
       </c>
       <c r="G24">
-        <v>-17.4935991314673</v>
+        <v>-14.55316265185001</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-14.35960911325869</v>
       </c>
       <c r="E25">
-        <v>-41.96733153503413</v>
+        <v>-39.30907200779155</v>
       </c>
       <c r="F25">
-        <v>-3.855532696166664</v>
+        <v>-3.237673588846695</v>
       </c>
       <c r="G25">
-        <v>-16.83803166159866</v>
+        <v>-15.06706856754769</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-14.18659311104872</v>
       </c>
       <c r="E26">
-        <v>-42.05766553453913</v>
+        <v>-39.65366623740523</v>
       </c>
       <c r="F26">
-        <v>-3.863754505426668</v>
+        <v>-2.963512714854268</v>
       </c>
       <c r="G26">
-        <v>-17.07746355718091</v>
+        <v>-15.42965275719083</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.99251818878793</v>
       </c>
       <c r="E27">
-        <v>-41.6882416819414</v>
+        <v>-39.29139963797662</v>
       </c>
       <c r="F27">
-        <v>-3.949916817609109</v>
+        <v>-3.041092924680943</v>
       </c>
       <c r="G27">
-        <v>-17.4050801095655</v>
+        <v>-15.89197375229559</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-13.78059942755858</v>
       </c>
       <c r="E28">
-        <v>-41.68571252920812</v>
+        <v>-38.39086729681129</v>
       </c>
       <c r="F28">
-        <v>-3.680762829868344</v>
+        <v>-3.023333246545205</v>
       </c>
       <c r="G28">
-        <v>-17.59131815942273</v>
+        <v>-15.63908283382344</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-13.5542585294597</v>
       </c>
       <c r="E29">
-        <v>-41.91833797474514</v>
+        <v>-37.85427709045741</v>
       </c>
       <c r="F29">
-        <v>-3.80516055396724</v>
+        <v>-3.001316566908766</v>
       </c>
       <c r="G29">
-        <v>-17.51251558867869</v>
+        <v>-15.94021833243939</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-13.31518403037692</v>
       </c>
       <c r="E30">
-        <v>-41.35498901547994</v>
+        <v>-39.68826830729783</v>
       </c>
       <c r="F30">
-        <v>-3.714054703769754</v>
+        <v>-2.866950205925137</v>
       </c>
       <c r="G30">
-        <v>-17.52772754543165</v>
+        <v>-15.40902971375394</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.06494172848005</v>
       </c>
       <c r="E31">
-        <v>-40.99248240692892</v>
+        <v>-38.44949744978859</v>
       </c>
       <c r="F31">
-        <v>-3.737095249280525</v>
+        <v>-3.139159954229742</v>
       </c>
       <c r="G31">
-        <v>-17.62732365270785</v>
+        <v>-16.01897786609142</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.80536096661462</v>
       </c>
       <c r="E32">
-        <v>-41.2802827797754</v>
+        <v>-38.24849207401013</v>
       </c>
       <c r="F32">
-        <v>-3.907570105136173</v>
+        <v>-2.898780319266597</v>
       </c>
       <c r="G32">
-        <v>-17.46984265667749</v>
+        <v>-16.5424512583976</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.53852311469598</v>
       </c>
       <c r="E33">
-        <v>-41.07351492082218</v>
+        <v>-37.50834922524847</v>
       </c>
       <c r="F33">
-        <v>-3.720737942732909</v>
+        <v>-2.994597694562514</v>
       </c>
       <c r="G33">
-        <v>-17.58380487632136</v>
+        <v>-15.72996061942197</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.26688571929664</v>
       </c>
       <c r="E34">
-        <v>-40.81468998891378</v>
+        <v>-38.21023326135633</v>
       </c>
       <c r="F34">
-        <v>-3.921310337658526</v>
+        <v>-2.693603299391839</v>
       </c>
       <c r="G34">
-        <v>-17.62846413564613</v>
+        <v>-15.33687471845276</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.9931506195948</v>
       </c>
       <c r="E35">
-        <v>-40.16775219217799</v>
+        <v>-37.06850080912046</v>
       </c>
       <c r="F35">
-        <v>-3.725381368476977</v>
+        <v>-3.457727942091091</v>
       </c>
       <c r="G35">
-        <v>-17.7854866211193</v>
+        <v>-16.7737524541354</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.71846454256618</v>
       </c>
       <c r="E36">
-        <v>-40.11984546565084</v>
+        <v>-37.03580069831107</v>
       </c>
       <c r="F36">
-        <v>-3.782804961264896</v>
+        <v>-3.36252979580811</v>
       </c>
       <c r="G36">
-        <v>-18.08428156403899</v>
+        <v>-15.53288549874193</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.44645374698229</v>
       </c>
       <c r="E37">
-        <v>-39.6023450414763</v>
+        <v>-36.3643729141418</v>
       </c>
       <c r="F37">
-        <v>-3.868380510405667</v>
+        <v>-3.248715186489139</v>
       </c>
       <c r="G37">
-        <v>-18.13774852977099</v>
+        <v>-15.91250078991184</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.18084043299429</v>
       </c>
       <c r="E38">
-        <v>-39.14289512560607</v>
+        <v>-37.39031455023854</v>
       </c>
       <c r="F38">
-        <v>-4.034489089052449</v>
+        <v>-3.182673066109399</v>
       </c>
       <c r="G38">
-        <v>-17.71280028325906</v>
+        <v>-16.73444965749317</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.92466096923624</v>
       </c>
       <c r="E39">
-        <v>-39.08493518678191</v>
+        <v>-35.17882294740771</v>
       </c>
       <c r="F39">
-        <v>-3.859069903328798</v>
+        <v>-2.990225874382944</v>
       </c>
       <c r="G39">
-        <v>-18.0452816823136</v>
+        <v>-15.27771692493875</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.68088165702687</v>
       </c>
       <c r="E40">
-        <v>-38.6297465649529</v>
+        <v>-34.65025493275841</v>
       </c>
       <c r="F40">
-        <v>-3.756566121657895</v>
+        <v>-2.792021119800908</v>
       </c>
       <c r="G40">
-        <v>-17.95354315487486</v>
+        <v>-15.66059806928316</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.45158289779922</v>
       </c>
       <c r="E41">
-        <v>-38.28053782032541</v>
+        <v>-35.31791955502731</v>
       </c>
       <c r="F41">
-        <v>-3.710999735058872</v>
+        <v>-3.000430483449077</v>
       </c>
       <c r="G41">
-        <v>-18.13581848172159</v>
+        <v>-16.2714152398247</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.23712694720114</v>
       </c>
       <c r="E42">
-        <v>-38.39709621280884</v>
+        <v>-35.38754031442124</v>
       </c>
       <c r="F42">
-        <v>-3.694757247190124</v>
+        <v>-3.225558238593583</v>
       </c>
       <c r="G42">
-        <v>-18.40900635489502</v>
+        <v>-16.26304121488311</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.04176248807751</v>
       </c>
       <c r="E43">
-        <v>-37.7600440748318</v>
+        <v>-34.37385952170025</v>
       </c>
       <c r="F43">
-        <v>-3.776600001488204</v>
+        <v>-3.0032843215087</v>
       </c>
       <c r="G43">
-        <v>-18.42455598729298</v>
+        <v>-16.37280731805596</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.866247200783437</v>
       </c>
       <c r="E44">
-        <v>-36.76279485004765</v>
+        <v>-34.13694334704097</v>
       </c>
       <c r="F44">
-        <v>-3.889667101615088</v>
+        <v>-3.152441703889575</v>
       </c>
       <c r="G44">
-        <v>-18.30675187955078</v>
+        <v>-16.06691456550007</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.71068921717927</v>
       </c>
       <c r="E45">
-        <v>-36.45819610286972</v>
+        <v>-33.02760306938196</v>
       </c>
       <c r="F45">
-        <v>-3.852511777132964</v>
+        <v>-3.386075543505906</v>
       </c>
       <c r="G45">
-        <v>-18.21810705691849</v>
+        <v>-16.09239914506138</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.574270615750779</v>
       </c>
       <c r="E46">
-        <v>-36.25570765185374</v>
+        <v>-32.85413534404414</v>
       </c>
       <c r="F46">
-        <v>-3.950842493716683</v>
+        <v>-3.755186713805548</v>
       </c>
       <c r="G46">
-        <v>-18.14101603821825</v>
+        <v>-15.95388757497104</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.455441272810855</v>
       </c>
       <c r="E47">
-        <v>-35.79097300681657</v>
+        <v>-32.74133105651307</v>
       </c>
       <c r="F47">
-        <v>-4.000585112814721</v>
+        <v>-3.390989782961515</v>
       </c>
       <c r="G47">
-        <v>-18.16354761115853</v>
+        <v>-15.34371265026412</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.35239775529999</v>
       </c>
       <c r="E48">
-        <v>-35.71912423821087</v>
+        <v>-33.24479773973784</v>
       </c>
       <c r="F48">
-        <v>-4.097035970476814</v>
+        <v>-3.422035170021875</v>
       </c>
       <c r="G48">
-        <v>-18.69860956812493</v>
+        <v>-15.81076938076281</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.263157731890995</v>
       </c>
       <c r="E49">
-        <v>-34.78359584991427</v>
+        <v>-31.82180629535957</v>
       </c>
       <c r="F49">
-        <v>-3.873191808976772</v>
+        <v>-3.299360517958977</v>
       </c>
       <c r="G49">
-        <v>-18.35873075506288</v>
+        <v>-16.04518745512583</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.185266968635744</v>
       </c>
       <c r="E50">
-        <v>-34.77209805440879</v>
+        <v>-31.79043982014544</v>
       </c>
       <c r="F50">
-        <v>-3.988443631414004</v>
+        <v>-3.158032977624034</v>
       </c>
       <c r="G50">
-        <v>-18.10729813190077</v>
+        <v>-16.19016783119991</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.115890816925168</v>
       </c>
       <c r="E51">
-        <v>-34.47629360375376</v>
+        <v>-31.66435804682389</v>
       </c>
       <c r="F51">
-        <v>-3.928670610900531</v>
+        <v>-3.408051838641502</v>
       </c>
       <c r="G51">
-        <v>-18.52316389672571</v>
+        <v>-15.82979674124977</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.054982981645585</v>
       </c>
       <c r="E52">
-        <v>-34.16846379037136</v>
+        <v>-30.49349165705966</v>
       </c>
       <c r="F52">
-        <v>-3.869633221784779</v>
+        <v>-3.548859923436181</v>
       </c>
       <c r="G52">
-        <v>-18.35697120010876</v>
+        <v>-15.97751493848482</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.00156176385231</v>
       </c>
       <c r="E53">
-        <v>-34.10449003806499</v>
+        <v>-31.21468963481023</v>
       </c>
       <c r="F53">
-        <v>-3.946552234391758</v>
+        <v>-3.47201138574244</v>
       </c>
       <c r="G53">
-        <v>-18.66446460143288</v>
+        <v>-15.82983150197793</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.954852516444095</v>
       </c>
       <c r="E54">
-        <v>-33.07371878443907</v>
+        <v>-31.07608889509447</v>
       </c>
       <c r="F54">
-        <v>-3.911796224371524</v>
+        <v>-3.393639322958045</v>
       </c>
       <c r="G54">
-        <v>-18.62799728704504</v>
+        <v>-15.7858624913981</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.914476092089052</v>
       </c>
       <c r="E55">
-        <v>-32.88037558668158</v>
+        <v>-30.11995142158896</v>
       </c>
       <c r="F55">
-        <v>-4.023768983710839</v>
+        <v>-3.618118550530179</v>
       </c>
       <c r="G55">
-        <v>-18.85785177438218</v>
+        <v>-16.0556504343027</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.878649451420737</v>
       </c>
       <c r="E56">
-        <v>-32.84003141174725</v>
+        <v>-29.27362944276945</v>
       </c>
       <c r="F56">
-        <v>-4.127893688386194</v>
+        <v>-3.393591811780582</v>
       </c>
       <c r="G56">
-        <v>-18.57583798680106</v>
+        <v>-16.57944826007173</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.848548742707683</v>
       </c>
       <c r="E57">
-        <v>-32.53904638682744</v>
+        <v>-29.93309299861046</v>
       </c>
       <c r="F57">
-        <v>-4.106261057434248</v>
+        <v>-3.82322826290353</v>
       </c>
       <c r="G57">
-        <v>-18.71605448784412</v>
+        <v>-16.39041445450657</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.824611427068454</v>
       </c>
       <c r="E58">
-        <v>-32.30535222142461</v>
+        <v>-29.71917241496212</v>
       </c>
       <c r="F58">
-        <v>-4.294987332112379</v>
+        <v>-3.656796608249999</v>
       </c>
       <c r="G58">
-        <v>-18.73571581780185</v>
+        <v>-16.09475128766703</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.806488386830353</v>
       </c>
       <c r="E59">
-        <v>-31.76668570973821</v>
+        <v>-28.79871931663705</v>
       </c>
       <c r="F59">
-        <v>-4.256225337979041</v>
+        <v>-3.921197102685572</v>
       </c>
       <c r="G59">
-        <v>-18.95210631643077</v>
+        <v>-16.49656378667776</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.793871162333984</v>
       </c>
       <c r="E60">
-        <v>-31.50091409870204</v>
+        <v>-28.32316614719555</v>
       </c>
       <c r="F60">
-        <v>-4.259604174549631</v>
+        <v>-3.72659923832595</v>
       </c>
       <c r="G60">
-        <v>-18.92962440167358</v>
+        <v>-15.61071311382465</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.786224897031191</v>
       </c>
       <c r="E61">
-        <v>-31.47765812043565</v>
+        <v>-27.74138856295614</v>
       </c>
       <c r="F61">
-        <v>-4.279536697201352</v>
+        <v>-3.43969507468494</v>
       </c>
       <c r="G61">
-        <v>-18.918447999933</v>
+        <v>-15.61708094816944</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.783047366122988</v>
       </c>
       <c r="E62">
-        <v>-31.01164418149131</v>
+        <v>-28.93820990149532</v>
       </c>
       <c r="F62">
-        <v>-4.452360980782554</v>
+        <v>-4.007307152572803</v>
       </c>
       <c r="G62">
-        <v>-19.13487491456285</v>
+        <v>-16.23018736095139</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.783549468301059</v>
       </c>
       <c r="E63">
-        <v>-30.74334115348486</v>
+        <v>-28.26706741118853</v>
       </c>
       <c r="F63">
-        <v>-4.314593611345519</v>
+        <v>-3.749022138529699</v>
       </c>
       <c r="G63">
-        <v>-18.80557660504432</v>
+        <v>-16.57622709926202</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.786747630859152</v>
       </c>
       <c r="E64">
-        <v>-31.02588623224544</v>
+        <v>-27.39288626027384</v>
       </c>
       <c r="F64">
-        <v>-4.4956420797456</v>
+        <v>-4.065791828324067</v>
       </c>
       <c r="G64">
-        <v>-19.01157199067993</v>
+        <v>-16.43069882790119</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.789727810598031</v>
       </c>
       <c r="E65">
-        <v>-30.48804390282844</v>
+        <v>-27.72333806556156</v>
       </c>
       <c r="F65">
-        <v>-4.542960045087099</v>
+        <v>-4.038935343410045</v>
       </c>
       <c r="G65">
-        <v>-19.14503663409565</v>
+        <v>-15.89916425720689</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.792426881963447</v>
       </c>
       <c r="E66">
-        <v>-31.13146986797128</v>
+        <v>-27.66886505172329</v>
       </c>
       <c r="F66">
-        <v>-4.590797465968863</v>
+        <v>-4.071376767234864</v>
       </c>
       <c r="G66">
-        <v>-18.86174166539082</v>
+        <v>-16.56098534759921</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.793888753172149</v>
       </c>
       <c r="E67">
-        <v>-30.50696839570649</v>
+        <v>-27.40453802389558</v>
       </c>
       <c r="F67">
-        <v>-4.596123468962486</v>
+        <v>-4.282489516880688</v>
       </c>
       <c r="G67">
-        <v>-19.06252128652931</v>
+        <v>-15.90023687396161</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.793042335874363</v>
       </c>
       <c r="E68">
-        <v>-30.63335810526057</v>
+        <v>-28.39246085646093</v>
       </c>
       <c r="F68">
-        <v>-4.491185531299553</v>
+        <v>-4.190657537520975</v>
       </c>
       <c r="G68">
-        <v>-18.83877144516659</v>
+        <v>-16.47193332786559</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.788977736972726</v>
       </c>
       <c r="E69">
-        <v>-30.48841523769707</v>
+        <v>-27.45748494199326</v>
       </c>
       <c r="F69">
-        <v>-4.628877674705604</v>
+        <v>-4.068817498475514</v>
       </c>
       <c r="G69">
-        <v>-19.04602649337989</v>
+        <v>-16.89453605286294</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.780567345518328</v>
       </c>
       <c r="E70">
-        <v>-30.13103712595974</v>
+        <v>-28.60063027811952</v>
       </c>
       <c r="F70">
-        <v>-4.758770066478117</v>
+        <v>-4.187859129168393</v>
       </c>
       <c r="G70">
-        <v>-18.9022792955192</v>
+        <v>-17.22471496749492</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.766743822292405</v>
       </c>
       <c r="E71">
-        <v>-30.73230979080218</v>
+        <v>-27.39815740401877</v>
       </c>
       <c r="F71">
-        <v>-4.810974556421706</v>
+        <v>-4.256829521785781</v>
       </c>
       <c r="G71">
-        <v>-18.83887572735108</v>
+        <v>-16.79179327205166</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.74866729655975</v>
       </c>
       <c r="E72">
-        <v>-30.77956215283521</v>
+        <v>-27.92794357817612</v>
       </c>
       <c r="F72">
-        <v>-4.916732061895878</v>
+        <v>-4.087642218839385</v>
       </c>
       <c r="G72">
-        <v>-18.5830152495302</v>
+        <v>-16.54572869848148</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.725938386961463</v>
       </c>
       <c r="E73">
-        <v>-31.37155823867294</v>
+        <v>-27.88308451465614</v>
       </c>
       <c r="F73">
-        <v>-4.991262845982375</v>
+        <v>-4.361529111708441</v>
       </c>
       <c r="G73">
-        <v>-18.47461640166507</v>
+        <v>-17.03785619034907</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.698230763959304</v>
       </c>
       <c r="E74">
-        <v>-31.35545724933867</v>
+        <v>-28.61324207823089</v>
       </c>
       <c r="F74">
-        <v>-4.88700590186308</v>
+        <v>-4.677986811437466</v>
       </c>
       <c r="G74">
-        <v>-19.07420089119186</v>
+        <v>-16.20288694716179</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.665290980112761</v>
       </c>
       <c r="E75">
-        <v>-31.67728004740477</v>
+        <v>-28.73749887652735</v>
       </c>
       <c r="F75">
-        <v>-4.89408348359918</v>
+        <v>-4.427605281765363</v>
       </c>
       <c r="G75">
-        <v>-18.6335871431881</v>
+        <v>-15.96295350393034</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.627079122436724</v>
       </c>
       <c r="E76">
-        <v>-32.03315697000856</v>
+        <v>-28.35072191153223</v>
       </c>
       <c r="F76">
-        <v>-5.004094031309265</v>
+        <v>-5.024021010990282</v>
       </c>
       <c r="G76">
-        <v>-18.54578154385001</v>
+        <v>-16.88455310278927</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.583934373226333</v>
       </c>
       <c r="E77">
-        <v>-31.69433880899167</v>
+        <v>-28.23161851665649</v>
       </c>
       <c r="F77">
-        <v>-5.324918800100115</v>
+        <v>-4.336181898531833</v>
       </c>
       <c r="G77">
-        <v>-18.28906032418892</v>
+        <v>-16.0556669870304</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.536422979087185</v>
       </c>
       <c r="E78">
-        <v>-31.84704121676732</v>
+        <v>-28.98550981250543</v>
       </c>
       <c r="F78">
-        <v>-5.255788453185268</v>
+        <v>-4.377556215572688</v>
       </c>
       <c r="G78">
-        <v>-17.93800841993183</v>
+        <v>-16.83517466079827</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.484421077470751</v>
       </c>
       <c r="E79">
-        <v>-32.00085989338585</v>
+        <v>-29.63258799193546</v>
       </c>
       <c r="F79">
-        <v>-5.236218599188183</v>
+        <v>-4.539034038122725</v>
       </c>
       <c r="G79">
-        <v>-17.82290571734968</v>
+        <v>-16.72361589721591</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.428241347891529</v>
       </c>
       <c r="E80">
-        <v>-33.13031565258693</v>
+        <v>-30.06589049888539</v>
       </c>
       <c r="F80">
-        <v>-5.167747073934158</v>
+        <v>-4.659569103493864</v>
       </c>
       <c r="G80">
-        <v>-17.87081427712124</v>
+        <v>-15.8847286233829</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.369563712489176</v>
       </c>
       <c r="E81">
-        <v>-33.06689210987251</v>
+        <v>-30.39199496912575</v>
       </c>
       <c r="F81">
-        <v>-5.188130952771779</v>
+        <v>-4.946211955658827</v>
       </c>
       <c r="G81">
-        <v>-17.57895989292464</v>
+        <v>-16.22345536659728</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.309165906031621</v>
       </c>
       <c r="E82">
-        <v>-33.90124759612674</v>
+        <v>-30.59744504214274</v>
       </c>
       <c r="F82">
-        <v>-5.324071517435355</v>
+        <v>-4.527452396763116</v>
       </c>
       <c r="G82">
-        <v>-17.7421863407384</v>
+        <v>-15.45562729749195</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.247552853697321</v>
       </c>
       <c r="E83">
-        <v>-34.06301148039174</v>
+        <v>-31.0989531603592</v>
       </c>
       <c r="F83">
-        <v>-5.42154940838361</v>
+        <v>-4.679724136826704</v>
       </c>
       <c r="G83">
-        <v>-17.52050062451941</v>
+        <v>-15.95897753873767</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.185163632478268</v>
       </c>
       <c r="E84">
-        <v>-34.40269231570709</v>
+        <v>-32.01397661834907</v>
       </c>
       <c r="F84">
-        <v>-5.449824101944909</v>
+        <v>-5.238678886327818</v>
       </c>
       <c r="G84">
-        <v>-18.0001556360678</v>
+        <v>-15.60243178415817</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.120606841791865</v>
       </c>
       <c r="E85">
-        <v>-35.94148363317251</v>
+        <v>-32.25673226024125</v>
       </c>
       <c r="F85">
-        <v>-5.456694218206085</v>
+        <v>-5.089953063808899</v>
       </c>
       <c r="G85">
-        <v>-17.51947932122055</v>
+        <v>-16.00335374641883</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.055375666010191</v>
       </c>
       <c r="E86">
-        <v>-36.09094818203267</v>
+        <v>-33.77094981350405</v>
       </c>
       <c r="F86">
-        <v>-5.604218007935185</v>
+        <v>-4.777707229961985</v>
       </c>
       <c r="G86">
-        <v>-17.67835571219571</v>
+        <v>-15.16521300060493</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.989232552470397</v>
       </c>
       <c r="E87">
-        <v>-36.48626132053226</v>
+        <v>-34.24218281874222</v>
       </c>
       <c r="F87">
-        <v>-5.667328688665447</v>
+        <v>-4.790374501726627</v>
       </c>
       <c r="G87">
-        <v>-17.28912659677975</v>
+        <v>-15.21205556471285</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.921186434360534</v>
       </c>
       <c r="E88">
-        <v>-37.39311767564929</v>
+        <v>-36.03784276734472</v>
       </c>
       <c r="F88">
-        <v>-5.424506187327736</v>
+        <v>-5.145278246258861</v>
       </c>
       <c r="G88">
-        <v>-17.53477073106644</v>
+        <v>-16.48317428524418</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.849842646031865</v>
       </c>
       <c r="E89">
-        <v>-38.44555541316492</v>
+        <v>-35.75373310081449</v>
       </c>
       <c r="F89">
-        <v>-5.663099402018266</v>
+        <v>-4.936217187626488</v>
       </c>
       <c r="G89">
-        <v>-17.21973590700386</v>
+        <v>-15.83828994583077</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.77337759448343</v>
       </c>
       <c r="E90">
-        <v>-39.82673998550437</v>
+        <v>-36.93716374171299</v>
       </c>
       <c r="F90">
-        <v>-5.620637079013504</v>
+        <v>-5.376578495208792</v>
       </c>
       <c r="G90">
-        <v>-17.72285937588014</v>
+        <v>-15.53591299263759</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.689654977978978</v>
       </c>
       <c r="E91">
-        <v>-40.63850970764536</v>
+        <v>-37.67676090935673</v>
       </c>
       <c r="F91">
-        <v>-5.750426529901513</v>
+        <v>-5.292370476126004</v>
       </c>
       <c r="G91">
-        <v>-17.31872287390084</v>
+        <v>-15.61638904415173</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.596471533296024</v>
       </c>
       <c r="E92">
-        <v>-41.50961828894584</v>
+        <v>-40.12668798987643</v>
       </c>
       <c r="F92">
-        <v>-5.595264526542248</v>
+        <v>-5.379020569730399</v>
       </c>
       <c r="G92">
-        <v>-17.46575082239095</v>
+        <v>-15.62599790257947</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.491585378590655</v>
       </c>
       <c r="E93">
-        <v>-42.77418786287679</v>
+        <v>-40.86121326663157</v>
       </c>
       <c r="F93">
-        <v>-5.67784607964988</v>
+        <v>-5.589107869795978</v>
       </c>
       <c r="G93">
-        <v>-17.68178212682886</v>
+        <v>-16.02025408139681</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.371612473490081</v>
       </c>
       <c r="E94">
-        <v>-43.59512095217229</v>
+        <v>-42.43243298646592</v>
       </c>
       <c r="F94">
-        <v>-5.728670369888163</v>
+        <v>-5.398239632867215</v>
       </c>
       <c r="G94">
-        <v>-17.43262881427054</v>
+        <v>-16.10970998768623</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.236078049626133</v>
       </c>
       <c r="E95">
-        <v>-44.91856295243994</v>
+        <v>-43.31854440215382</v>
       </c>
       <c r="F95">
-        <v>-5.810443441125964</v>
+        <v>-5.247881009549479</v>
       </c>
       <c r="G95">
-        <v>-17.94227405785918</v>
+        <v>-16.04433830019501</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.083103399621029</v>
       </c>
       <c r="E96">
-        <v>-45.4085053480408</v>
+        <v>-44.28077946591065</v>
       </c>
       <c r="F96">
-        <v>-5.775718313371081</v>
+        <v>-5.752014195081741</v>
       </c>
       <c r="G96">
-        <v>-17.98094619557618</v>
+        <v>-15.75069953195274</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.912123886201729</v>
       </c>
       <c r="E97">
-        <v>-47.05312031035447</v>
+        <v>-46.23057055583823</v>
       </c>
       <c r="F97">
-        <v>-5.914045522849223</v>
+        <v>-5.466844981271095</v>
       </c>
       <c r="G97">
-        <v>-17.84430839426107</v>
+        <v>-16.05110340000451</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.721136951073437</v>
       </c>
       <c r="E98">
-        <v>-48.77432761779686</v>
+        <v>-47.42371703772019</v>
       </c>
       <c r="F98">
-        <v>-5.991540212556465</v>
+        <v>-5.382324972122964</v>
       </c>
       <c r="G98">
-        <v>-18.26376113517781</v>
+        <v>-15.85079553160537</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.510789026917764</v>
       </c>
       <c r="E99">
-        <v>-50.22675414322499</v>
+        <v>-49.51879968770985</v>
       </c>
       <c r="F99">
-        <v>-6.025912965745162</v>
+        <v>-5.23920230113287</v>
       </c>
       <c r="G99">
-        <v>-18.11614887540001</v>
+        <v>-16.60246979375182</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.27846612972345</v>
       </c>
       <c r="E100">
-        <v>-51.71167246965815</v>
+        <v>-50.60703840861161</v>
       </c>
       <c r="F100">
-        <v>-6.173620069433975</v>
+        <v>-5.512943493057706</v>
       </c>
       <c r="G100">
-        <v>-18.37034745936018</v>
+        <v>-16.06002035441454</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.030835691427956</v>
       </c>
       <c r="E101">
-        <v>-52.8614769268127</v>
+        <v>-53.01803646232438</v>
       </c>
       <c r="F101">
-        <v>-6.177053543858647</v>
+        <v>-5.78032689758501</v>
       </c>
       <c r="G101">
-        <v>-18.59001705334575</v>
+        <v>-16.19719942992532</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.76226596714339</v>
       </c>
       <c r="E102">
-        <v>-54.18003609998158</v>
+        <v>-54.22885757825828</v>
       </c>
       <c r="F102">
-        <v>-6.281617726925536</v>
+        <v>-5.579959592575442</v>
       </c>
       <c r="G102">
-        <v>-18.382176038572</v>
+        <v>-17.85026737623176</v>
       </c>
     </row>
   </sheetData>
